--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2018.xlsx
@@ -15727,7 +15727,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cobertura APS de vejez</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2018.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="712">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Macrozona Austral</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Aysen</t>
@@ -508,18 +508,18 @@
     <t xml:space="preserve">Pumanque</t>
   </si>
   <si>
+    <t xml:space="preserve">6114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta de Tilcoco</t>
+  </si>
+  <si>
     <t xml:space="preserve">7405</t>
   </si>
   <si>
     <t xml:space="preserve">Retiro</t>
   </si>
   <si>
-    <t xml:space="preserve">6114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinta de Tilcoco</t>
-  </si>
-  <si>
     <t xml:space="preserve">6307</t>
   </si>
   <si>
@@ -607,18 +607,18 @@
     <t xml:space="preserve">El Bosque</t>
   </si>
   <si>
+    <t xml:space="preserve">5506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogales</t>
+  </si>
+  <si>
     <t xml:space="preserve">6202</t>
   </si>
   <si>
     <t xml:space="preserve">La Estrella</t>
   </si>
   <si>
-    <t xml:space="preserve">5506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogales</t>
-  </si>
-  <si>
     <t xml:space="preserve">6105</t>
   </si>
   <si>
@@ -751,18 +751,18 @@
     <t xml:space="preserve">María Pinto</t>
   </si>
   <si>
+    <t xml:space="preserve">5107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintero</t>
+  </si>
+  <si>
     <t xml:space="preserve">7107</t>
   </si>
   <si>
     <t xml:space="preserve">Pencahue</t>
   </si>
   <si>
-    <t xml:space="preserve">5107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quintero</t>
-  </si>
-  <si>
     <t xml:space="preserve">5504</t>
   </si>
   <si>
@@ -1312,15 +1312,15 @@
     <t xml:space="preserve">Monte Patria</t>
   </si>
   <si>
+    <t xml:space="preserve">3304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huasco</t>
+  </si>
+  <si>
     <t xml:space="preserve">4102</t>
   </si>
   <si>
-    <t xml:space="preserve">3304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huasco</t>
-  </si>
-  <si>
     <t xml:space="preserve">4301</t>
   </si>
   <si>
@@ -1369,18 +1369,18 @@
     <t xml:space="preserve">Chañaral</t>
   </si>
   <si>
+    <t xml:space="preserve">2103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sierra Gorda</t>
+  </si>
+  <si>
     <t xml:space="preserve">3101</t>
   </si>
   <si>
     <t xml:space="preserve">Copiapó</t>
   </si>
   <si>
-    <t xml:space="preserve">2103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sierra Gorda</t>
-  </si>
-  <si>
     <t xml:space="preserve">4202</t>
   </si>
   <si>
@@ -2107,7 +2107,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:27</t>
+    <t xml:space="preserve">2026-07-30 15:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2119,16 +2119,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_p_aps_a_2018.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Cobertura APS de vejez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -4829,10 +4838,10 @@
         <v>2018</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>163</v>
@@ -4861,10 +4870,10 @@
         <v>2018</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>165</v>
@@ -5373,10 +5382,10 @@
         <v>2018</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>196</v>
@@ -5405,10 +5414,10 @@
         <v>2018</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>198</v>
@@ -6141,10 +6150,10 @@
         <v>2018</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>244</v>
@@ -6173,10 +6182,10 @@
         <v>2018</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>246</v>
@@ -9021,16 +9030,16 @@
         <v>2018</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>431</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>395</v>
@@ -9053,16 +9062,16 @@
         <v>2018</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>395</v>
@@ -9341,10 +9350,10 @@
         <v>2018</v>
       </c>
       <c r="B214" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>450</v>
@@ -9373,10 +9382,10 @@
         <v>2018</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>452</v>
@@ -13229,23 +13238,23 @@
         <v>701</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>
@@ -13260,28 +13269,28 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13290,7 +13299,7 @@
         <v>2018</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2018.xlsx
@@ -2107,7 +2107,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:56</t>
+    <t xml:space="preserve">2026-09-07 13:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_p_aps_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_p_aps_a_2018.xlsx
@@ -2107,7 +2107,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 13:11</t>
+    <t xml:space="preserve">2026-09-08 10:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
